--- a/data/default/SoilC.xlsx
+++ b/data/default/SoilC.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07ED0364-646A-4EB1-A155-16599CB20CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B0FA31-CB9B-4141-8844-7558E5197785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1725" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
     <sheet name="check" sheetId="4" r:id="rId2"/>
     <sheet name="literature data" sheetId="3" r:id="rId3"/>
     <sheet name="references" sheetId="2" r:id="rId4"/>
+    <sheet name="re-values" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="169">
   <si>
     <t>f_region</t>
   </si>
@@ -270,12 +271,6 @@
     <t>https://doi.org/10.1080/17583004.2024.2304749</t>
   </si>
   <si>
-    <t>Thomas Kätterer, pers. com.</t>
-  </si>
-  <si>
-    <t>Deduced from re and re_crop assumption</t>
-  </si>
-  <si>
     <t>Fraction of below ground biomass C</t>
   </si>
   <si>
@@ -439,6 +434,133 @@
   </si>
   <si>
     <t>Same as manure?</t>
+  </si>
+  <si>
+    <t>Cereals, winter</t>
+  </si>
+  <si>
+    <t>Cereals, spring</t>
+  </si>
+  <si>
+    <t>Potatoes</t>
+  </si>
+  <si>
+    <t>Sugar beet</t>
+  </si>
+  <si>
+    <t>Green manure</t>
+  </si>
+  <si>
+    <t>Fallow</t>
+  </si>
+  <si>
+    <t>f_crop</t>
+  </si>
+  <si>
+    <t>Rapeseed, winter</t>
+  </si>
+  <si>
+    <t>Rapeseed, spring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green_fallow      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ley               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Root_crops        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter_cereals    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring_cereals    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter_oilseed    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring_oilseed    </t>
+  </si>
+  <si>
+    <t>Bolinder (pers. com.)</t>
+  </si>
+  <si>
+    <t>Vegetables</t>
+  </si>
+  <si>
+    <t>Grain legumes</t>
+  </si>
+  <si>
+    <t>Green_fallow</t>
+  </si>
+  <si>
+    <t>Root_crops</t>
+  </si>
+  <si>
+    <t>Seed_ley</t>
+  </si>
+  <si>
+    <t>Spring_cereals</t>
+  </si>
+  <si>
+    <t>Spring_oilseed</t>
+  </si>
+  <si>
+    <t>Winter_cereals</t>
+  </si>
+  <si>
+    <t>Winter_oilseed</t>
+  </si>
+  <si>
+    <t>Clay</t>
+  </si>
+  <si>
+    <t>Clay_loam</t>
+  </si>
+  <si>
+    <t>Loam</t>
+  </si>
+  <si>
+    <t>Loamy_sand</t>
+  </si>
+  <si>
+    <t>Sand</t>
+  </si>
+  <si>
+    <t>Sandy_clay_loam</t>
+  </si>
+  <si>
+    <t>Sandy_loam</t>
+  </si>
+  <si>
+    <t>Silt_loam</t>
+  </si>
+  <si>
+    <t>Silty_clay</t>
+  </si>
+  <si>
+    <t>Silty_clay_loam</t>
+  </si>
+  <si>
+    <t>PO8</t>
+  </si>
+  <si>
+    <t>Soil type</t>
+  </si>
+  <si>
+    <t>re_soil</t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>The re_clim and re_crop values are from re-values  supplied by Bolinder (pers.com.) for each region (PO8), crop and soil type.These were decomposed to re_clim, re_crop, and re_soil such that: re = re_clim * re_crop * re_soil
+This resulted in a good fit with small errors. re_soil was close to 1 (0.96 - 1.01) and is not used here.</t>
+  </si>
+  <si>
+    <t>See tab "re-values"</t>
   </si>
 </sst>
 </file>
@@ -452,7 +574,7 @@
     <numFmt numFmtId="167" formatCode="0.0000000"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,6 +665,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -653,7 +801,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -728,6 +876,20 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1329,6 +1491,72 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6701B419-54FF-13D3-188D-7132197BDF2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2800350" y="428625"/>
+          <a:ext cx="5610225" cy="2762250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1592,22 +1820,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="8" width="15.5703125" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="37.85546875" customWidth="1"/>
-    <col min="13" max="13" width="27.28515625" customWidth="1"/>
+    <col min="4" max="5" width="15.5703125" customWidth="1"/>
+    <col min="6" max="7" width="18.28515625" customWidth="1"/>
+    <col min="8" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="13" max="13" width="37.85546875" customWidth="1"/>
+    <col min="14" max="14" width="27.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>14</v>
@@ -1619,495 +1847,650 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>0.26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="2">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1.2525189999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" t="s">
+        <v>168</v>
+      </c>
+      <c r="N6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1.130498</v>
+      </c>
+      <c r="L7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1.1058490000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1.0451440000000001</v>
+      </c>
+      <c r="L9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1.1140810000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0.99563100000000004</v>
+      </c>
+      <c r="L11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.77713500000000002</v>
+      </c>
+      <c r="L12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.57914399999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0.78990099999999996</v>
+      </c>
+      <c r="L16" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="42" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>131</v>
+      </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0.86212800000000001</v>
+      </c>
+      <c r="L17" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="42" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.86212800000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="42" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>127</v>
+      </c>
+      <c r="J19" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0.976715</v>
+      </c>
+      <c r="L19" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>128</v>
+      </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1.065666</v>
+      </c>
+      <c r="L20" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F21" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1.065666</v>
+      </c>
+      <c r="L21" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1.2020090000000001</v>
+      </c>
+      <c r="L22" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="42" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+      <c r="J23" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1.2020090000000001</v>
+      </c>
+      <c r="L23" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="42" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1.2020090000000001</v>
+      </c>
+      <c r="L24" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="42" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.96538400000000002</v>
+      </c>
+      <c r="L25" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>135</v>
+      </c>
+      <c r="J26" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1.072751</v>
+      </c>
+      <c r="L26" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="42" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="J28" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28">
+        <v>0.09</v>
+      </c>
+      <c r="L28" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K29">
+        <v>0.36</v>
+      </c>
+      <c r="L29" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" t="s">
+        <v>10</v>
+      </c>
+      <c r="K30" s="24">
+        <f>K29</f>
+        <v>0.36</v>
+      </c>
+      <c r="L30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" t="s">
+        <v>10</v>
+      </c>
+      <c r="K31" s="24">
+        <f>K28</f>
+        <v>0.09</v>
+      </c>
+      <c r="L31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="24">
+        <f>K29</f>
+        <v>0.36</v>
+      </c>
+      <c r="L32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="J33" t="s">
+        <v>10</v>
+      </c>
+      <c r="K33" s="24">
+        <f>K30</f>
+        <v>0.36</v>
+      </c>
+      <c r="L33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>120</v>
+      </c>
+      <c r="J34" t="s">
+        <v>10</v>
+      </c>
+      <c r="K34">
+        <v>0.26</v>
+      </c>
+      <c r="L34" t="s">
+        <v>8</v>
+      </c>
+      <c r="N34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" t="s">
+        <v>10</v>
+      </c>
+      <c r="K35">
+        <v>0.26</v>
+      </c>
+      <c r="L35" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" t="s">
+        <v>126</v>
+      </c>
+      <c r="N35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>121</v>
+      </c>
+      <c r="J36" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36">
+        <v>0.26</v>
+      </c>
+      <c r="L36" t="s">
+        <v>8</v>
+      </c>
+      <c r="M36" t="s">
+        <v>126</v>
+      </c>
+      <c r="N36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J38" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38">
+        <v>0.65</v>
+      </c>
+      <c r="M38" t="s">
+        <v>72</v>
+      </c>
+      <c r="N38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" s="33" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J40" t="s">
+        <v>82</v>
+      </c>
+      <c r="K40" t="s">
         <v>124</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="I3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>0.26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="2">
-        <v>9.7000000000000003E-3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M4" t="s">
-        <v>69</v>
-      </c>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>8</v>
-      </c>
-      <c r="M6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7">
-        <v>0.8</v>
-      </c>
-      <c r="K7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="3">
-        <f>'literature data'!Y90</f>
-        <v>1.3301893968668552</v>
-      </c>
-      <c r="K9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="M9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="3">
-        <f>'literature data'!Y91</f>
-        <v>1.1255120030157393</v>
-      </c>
-      <c r="K10" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="3">
-        <f>'literature data'!Y92</f>
-        <v>1.081209522772449</v>
-      </c>
-      <c r="K11" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3">
-        <f>'literature data'!Y93</f>
-        <v>1.092531225341496</v>
-      </c>
-      <c r="K12" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="3">
-        <f>'literature data'!Y94</f>
-        <v>1.1204131825001622</v>
-      </c>
-      <c r="K13" t="s">
-        <v>8</v>
-      </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" s="3">
-        <f>'literature data'!Y95</f>
-        <v>0.97003505659264322</v>
-      </c>
-      <c r="K14" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="3">
-        <f>'literature data'!Y96</f>
-        <v>0.78943193471572826</v>
-      </c>
-      <c r="K15" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="3">
-        <f>'literature data'!Y97</f>
-        <v>0.7612582038754474</v>
-      </c>
-      <c r="K16" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="3"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18">
-        <v>0.09</v>
-      </c>
-      <c r="K18" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19">
-        <v>0.36</v>
-      </c>
-      <c r="K19" t="s">
-        <v>8</v>
-      </c>
-      <c r="M19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" s="24">
-        <f>J19</f>
-        <v>0.36</v>
-      </c>
-      <c r="K20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>121</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="24">
-        <f>J18</f>
-        <v>0.09</v>
-      </c>
-      <c r="K21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="24">
-        <f>J19</f>
-        <v>0.36</v>
-      </c>
-      <c r="K22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B23" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J23" s="24">
-        <f>J20</f>
-        <v>0.36</v>
-      </c>
-      <c r="K23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <v>0.26</v>
-      </c>
-      <c r="K24" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <v>0.26</v>
-      </c>
-      <c r="K25" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" t="s">
-        <v>128</v>
-      </c>
-      <c r="M25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>123</v>
-      </c>
-      <c r="I26" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26">
-        <v>0.26</v>
-      </c>
-      <c r="K26" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" t="s">
-        <v>128</v>
-      </c>
-      <c r="M26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I28" t="s">
-        <v>41</v>
-      </c>
-      <c r="J28">
-        <v>0.65</v>
-      </c>
-      <c r="L28" t="s">
-        <v>74</v>
-      </c>
-      <c r="M28" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="33" t="s">
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J41" s="27" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I30" t="s">
-        <v>84</v>
-      </c>
-      <c r="J30" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I31" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="J31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="I32" s="40" t="s">
+      <c r="K41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J42" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="K42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J43" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="K43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J44" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="J32" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I33" s="40" t="s">
+      <c r="K44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J45" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="J33" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I34" s="40" t="s">
+      <c r="K45" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J46" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="J34" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I35" s="40" t="s">
+      <c r="K46" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J47" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="J35" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I36" s="40" t="s">
+      <c r="K47" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J48" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="J36" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I37" s="40" t="s">
+      <c r="K48" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J49" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="J37" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="38" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I38" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="J38" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="39" spans="9:10" x14ac:dyDescent="0.25">
-      <c r="I39" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="J39" t="s">
-        <v>126</v>
+      <c r="K49" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -2128,31 +2511,31 @@
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="D1" s="33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="Q1" s="33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H2" s="32"/>
       <c r="I2" s="31" t="s">
@@ -2165,94 +2548,94 @@
       <c r="N2" s="32"/>
       <c r="O2" s="32"/>
       <c r="Q2" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="R2" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="S2" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="R2" s="26" t="s">
+      <c r="T2" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="S2" s="26" t="s">
+      <c r="U2" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="T2" s="26" t="s">
+      <c r="V2" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="U2" s="26" t="s">
+      <c r="W2" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="V2" s="26" t="s">
+      <c r="X2" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="W2" s="26" t="s">
+      <c r="Y2" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="X2" s="26" t="s">
+      <c r="Z2" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="26" t="s">
+      <c r="AA2" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="Z2" s="26" t="s">
+      <c r="AB2" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="AA2" s="26" t="s">
+      <c r="AC2" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="AB2" s="26" t="s">
+      <c r="AD2" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE2" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="AC2" s="26" t="s">
+      <c r="AF2" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="AD2" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE2" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AF2" s="26" t="s">
+      <c r="AG2" s="26" t="s">
         <v>116</v>
-      </c>
-      <c r="AG2" s="26" t="s">
-        <v>118</v>
       </c>
       <c r="AJ2" s="26"/>
       <c r="AK2" s="26"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" s="27"/>
       <c r="D3" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="G3" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="H3" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="I3" s="26" t="s">
         <v>83</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>85</v>
       </c>
       <c r="J3" s="27"/>
       <c r="K3" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="M3" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="N3" s="26" t="s">
         <v>87</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="N3" s="26" t="s">
-        <v>89</v>
       </c>
       <c r="O3" s="26"/>
       <c r="Q3" s="27"/>
@@ -2274,7 +2657,7 @@
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" s="27"/>
       <c r="D4" s="27"/>
@@ -2283,20 +2666,20 @@
       <c r="G4" s="27"/>
       <c r="H4" s="27"/>
       <c r="I4" s="27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J4" s="27"/>
       <c r="K4" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O4" s="27"/>
       <c r="Q4" s="27"/>
@@ -2318,7 +2701,7 @@
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B5" s="28">
         <v>6116.38644635124</v>
@@ -2426,7 +2809,7 @@
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" s="28">
         <v>4173.7878388872596</v>
@@ -2541,7 +2924,7 @@
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B7" s="28">
         <v>5378.7223225365997</v>
@@ -2655,7 +3038,7 @@
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B8" s="28">
         <v>4336.6779665245904</v>
@@ -3147,8 +3530,8 @@
         <v>38161</v>
       </c>
       <c r="Y90" s="3">
-        <f>F90/((W90*default!$J$7+(V90-W90)*1)/V90)</f>
-        <v>1.3301893968668552</v>
+        <f>F90/((W90*default!$K$16+(V90-W90)*1)/V90)</f>
+        <v>1.3317510425546617</v>
       </c>
     </row>
     <row r="91" spans="2:25" x14ac:dyDescent="0.25">
@@ -3211,8 +3594,8 @@
         <v>107979</v>
       </c>
       <c r="Y91" s="3">
-        <f>F91/((W91*default!$J$7+(V91-W91)*1)/V91)</f>
-        <v>1.1255120030157393</v>
+        <f>F91/((W91*default!$K$16+(V91-W91)*1)/V91)</f>
+        <v>1.1296140928763825</v>
       </c>
     </row>
     <row r="92" spans="2:25" x14ac:dyDescent="0.25">
@@ -3275,8 +3658,8 @@
         <v>85877</v>
       </c>
       <c r="Y92" s="3">
-        <f>F92/((W92*default!$J$7+(V92-W92)*1)/V92)</f>
-        <v>1.081209522772449</v>
+        <f>F92/((W92*default!$K$16+(V92-W92)*1)/V92)</f>
+        <v>1.0833771884909</v>
       </c>
     </row>
     <row r="93" spans="2:25" x14ac:dyDescent="0.25">
@@ -3339,8 +3722,8 @@
         <v>148894</v>
       </c>
       <c r="Y93" s="3">
-        <f>F93/((W93*default!$J$7+(V93-W93)*1)/V93)</f>
-        <v>1.092531225341496</v>
+        <f>F93/((W93*default!$K$16+(V93-W93)*1)/V93)</f>
+        <v>1.0953248980702073</v>
       </c>
     </row>
     <row r="94" spans="2:25" x14ac:dyDescent="0.25">
@@ -3403,8 +3786,8 @@
         <v>288509</v>
       </c>
       <c r="Y94" s="3">
-        <f>F94/((W94*default!$J$7+(V94-W94)*1)/V94)</f>
-        <v>1.1204131825001622</v>
+        <f>F94/((W94*default!$K$16+(V94-W94)*1)/V94)</f>
+        <v>1.1279157747794732</v>
       </c>
     </row>
     <row r="95" spans="2:25" x14ac:dyDescent="0.25">
@@ -3467,8 +3850,8 @@
         <v>90882</v>
       </c>
       <c r="Y95" s="3">
-        <f>F95/((W95*default!$J$7+(V95-W95)*1)/V95)</f>
-        <v>0.97003505659264322</v>
+        <f>F95/((W95*default!$K$16+(V95-W95)*1)/V95)</f>
+        <v>0.97507254750430528</v>
       </c>
     </row>
     <row r="96" spans="2:25" x14ac:dyDescent="0.25">
@@ -3531,8 +3914,8 @@
         <v>99489</v>
       </c>
       <c r="Y96" s="3">
-        <f>F96/((W96*default!$J$7+(V96-W96)*1)/V96)</f>
-        <v>0.78943193471572826</v>
+        <f>F96/((W96*default!$K$16+(V96-W96)*1)/V96)</f>
+        <v>0.79521837643289905</v>
       </c>
     </row>
     <row r="97" spans="2:25" x14ac:dyDescent="0.25">
@@ -3595,8 +3978,8 @@
         <v>69835</v>
       </c>
       <c r="Y97" s="3">
-        <f>F97/((W97*default!$J$7+(V97-W97)*1)/V97)</f>
-        <v>0.7612582038754474</v>
+        <f>F97/((W97*default!$K$16+(V97-W97)*1)/V97)</f>
+        <v>0.76653019606810968</v>
       </c>
     </row>
     <row r="99" spans="2:25" x14ac:dyDescent="0.25">
@@ -3787,13 +4170,13 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3807,4 +4190,355 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6256BD30-8B79-411B-A7CA-5A4E780F72D3}">
+  <dimension ref="B2:M34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="33"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="29">
+        <v>0.95851375749909495</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="29">
+        <v>0.86212839440338496</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="29">
+        <v>0.78990088673100001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="29">
+        <v>1.2020085492406301</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="29">
+        <v>1.10693250626238</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="29">
+        <v>1.06566623968096</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="29">
+        <v>1.0727508053302099</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="29">
+        <v>0.97671504783837104</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="29">
+        <v>0.96538381301394405</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="27"/>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="40">
+        <v>1</v>
+      </c>
+      <c r="C15" s="29">
+        <v>1.25251873205769</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="40">
+        <v>2</v>
+      </c>
+      <c r="C16" s="29">
+        <v>1.1304976130851601</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="40">
+        <v>3</v>
+      </c>
+      <c r="C17" s="29">
+        <v>1.1058493509157199</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="40">
+        <v>4</v>
+      </c>
+      <c r="C18" s="29">
+        <v>1.04514397374876</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="40">
+        <v>5</v>
+      </c>
+      <c r="C19" s="29">
+        <v>1.11408113931036</v>
+      </c>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="40">
+        <v>6</v>
+      </c>
+      <c r="C20" s="29">
+        <v>0.99563071605849696</v>
+      </c>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="40">
+        <v>7</v>
+      </c>
+      <c r="C21" s="29">
+        <v>0.77713470614039304</v>
+      </c>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="40">
+        <v>8</v>
+      </c>
+      <c r="C22" s="29">
+        <v>0.57914376868339201</v>
+      </c>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C23" s="27"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="29">
+        <v>0.98043487380979899</v>
+      </c>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="29">
+        <v>0.97091371731276999</v>
+      </c>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="29">
+        <v>0.99192382757576902</v>
+      </c>
+      <c r="E27" s="43"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="29">
+        <v>0.97949250511372998</v>
+      </c>
+      <c r="E28" s="43"/>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="29">
+        <v>1.0018524100973101</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C30" s="29">
+        <v>0.95741818761936703</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="29">
+        <v>0.98680909169685405</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="29">
+        <v>1.0054662408717201</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" s="29">
+        <v>0.97471458593920801</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="29">
+        <v>0.98362858614432902</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E18:M22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>